--- a/docs/REFERENCIA_SUMULA.xlsx
+++ b/docs/REFERENCIA_SUMULA.xlsx
@@ -2736,7 +2736,7 @@
       <xdr:row>1</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2571750" cy="1038225"/>
+    <xdr:ext cx="2571750" cy="853555"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="0" name="image1.jpg" title="Imagem"/>
